--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404703</v>
+        <v>122404640</v>
       </c>
       <c r="B2" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563708</v>
       </c>
       <c r="R2" t="n">
-        <v>6992367</v>
+        <v>6992337</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404640</v>
+        <v>122404710</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563708</v>
+        <v>563830</v>
       </c>
       <c r="R3" t="n">
-        <v>6992337</v>
+        <v>6992367</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,7 +882,7 @@
         <v>122404662</v>
       </c>
       <c r="B4" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,7 +984,7 @@
         <v>122404733</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404640</v>
+        <v>122404703</v>
       </c>
       <c r="B2" t="n">
         <v>79727</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563708</v>
+        <v>563830</v>
       </c>
       <c r="R2" t="n">
-        <v>6992337</v>
+        <v>6992367</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404710</v>
+        <v>122404662</v>
       </c>
       <c r="B3" t="n">
         <v>79727</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563830</v>
+        <v>563938</v>
       </c>
       <c r="R3" t="n">
-        <v>6992367</v>
+        <v>6992226</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404662</v>
+        <v>122404640</v>
       </c>
       <c r="B4" t="n">
         <v>79727</v>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563938</v>
+        <v>563708</v>
       </c>
       <c r="R4" t="n">
-        <v>6992226</v>
+        <v>6992337</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404703</v>
+        <v>122404662</v>
       </c>
       <c r="B2" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563938</v>
       </c>
       <c r="R2" t="n">
-        <v>6992367</v>
+        <v>6992226</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404662</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563938</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992226</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +882,7 @@
         <v>122404640</v>
       </c>
       <c r="B4" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404733</v>
+        <v>122404710</v>
       </c>
       <c r="B5" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563908</v>
+        <v>563830</v>
       </c>
       <c r="R5" t="n">
-        <v>6992177</v>
+        <v>6992367</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404662</v>
+        <v>122404710</v>
       </c>
       <c r="B2" t="n">
         <v>79732</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563938</v>
+        <v>563830</v>
       </c>
       <c r="R2" t="n">
-        <v>6992226</v>
+        <v>6992367</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404733</v>
+        <v>122404640</v>
       </c>
       <c r="B3" t="n">
         <v>79732</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563908</v>
+        <v>563708</v>
       </c>
       <c r="R3" t="n">
-        <v>6992177</v>
+        <v>6992337</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404640</v>
+        <v>122404674</v>
       </c>
       <c r="B4" t="n">
         <v>79732</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563708</v>
+        <v>563938</v>
       </c>
       <c r="R4" t="n">
-        <v>6992337</v>
+        <v>6992226</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404710</v>
+        <v>122404733</v>
       </c>
       <c r="B5" t="n">
         <v>79732</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563830</v>
+        <v>563908</v>
       </c>
       <c r="R5" t="n">
-        <v>6992367</v>
+        <v>6992177</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404710</v>
+        <v>122404640</v>
       </c>
       <c r="B2" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>6458</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563708</v>
       </c>
       <c r="R2" t="n">
-        <v>6992367</v>
+        <v>6992337</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404640</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>6458</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563708</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992337</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404674</v>
+        <v>122404710</v>
       </c>
       <c r="B4" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,11 +887,6 @@
       <c r="E4" t="n">
         <v>6458</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563938</v>
+        <v>563830</v>
       </c>
       <c r="R4" t="n">
-        <v>6992226</v>
+        <v>6992367</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404733</v>
+        <v>122404674</v>
       </c>
       <c r="B5" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1004,11 +984,6 @@
       <c r="E5" t="n">
         <v>6458</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1026,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563908</v>
+        <v>563938</v>
       </c>
       <c r="R5" t="n">
-        <v>6992177</v>
+        <v>6992226</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404640</v>
+        <v>122404710</v>
       </c>
       <c r="B2" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>6458</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563708</v>
+        <v>563830</v>
       </c>
       <c r="R2" t="n">
-        <v>6992337</v>
+        <v>6992367</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404733</v>
+        <v>122404674</v>
       </c>
       <c r="B3" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>6458</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -807,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563908</v>
+        <v>563938</v>
       </c>
       <c r="R3" t="n">
-        <v>6992177</v>
+        <v>6992226</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404710</v>
+        <v>122404733</v>
       </c>
       <c r="B4" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -887,6 +902,11 @@
       <c r="E4" t="n">
         <v>6458</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -904,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563830</v>
+        <v>563908</v>
       </c>
       <c r="R4" t="n">
-        <v>6992367</v>
+        <v>6992177</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404674</v>
+        <v>122404640</v>
       </c>
       <c r="B5" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -984,6 +1004,11 @@
       <c r="E5" t="n">
         <v>6458</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -1001,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563938</v>
+        <v>563708</v>
       </c>
       <c r="R5" t="n">
-        <v>6992226</v>
+        <v>6992337</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1037,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404710</v>
+        <v>122404662</v>
       </c>
       <c r="B2" t="n">
         <v>79737</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563938</v>
       </c>
       <c r="R2" t="n">
-        <v>6992367</v>
+        <v>6992226</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404674</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563938</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992226</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404733</v>
+        <v>122404710</v>
       </c>
       <c r="B4" t="n">
         <v>79737</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563908</v>
+        <v>563830</v>
       </c>
       <c r="R4" t="n">
-        <v>6992177</v>
+        <v>6992367</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404662</v>
+        <v>122404703</v>
       </c>
       <c r="B2" t="n">
         <v>79737</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563938</v>
+        <v>563830</v>
       </c>
       <c r="R2" t="n">
-        <v>6992226</v>
+        <v>6992367</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404733</v>
+        <v>122404674</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563908</v>
+        <v>563938</v>
       </c>
       <c r="R3" t="n">
-        <v>6992177</v>
+        <v>6992226</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404710</v>
+        <v>122404733</v>
       </c>
       <c r="B4" t="n">
         <v>79737</v>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563830</v>
+        <v>563908</v>
       </c>
       <c r="R4" t="n">
-        <v>6992367</v>
+        <v>6992177</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404674</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563938</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992226</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404733</v>
+        <v>122404640</v>
       </c>
       <c r="B4" t="n">
         <v>79737</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563908</v>
+        <v>563708</v>
       </c>
       <c r="R4" t="n">
-        <v>6992177</v>
+        <v>6992337</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404640</v>
+        <v>122404662</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1031,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563708</v>
+        <v>563938</v>
       </c>
       <c r="R5" t="n">
-        <v>6992337</v>
+        <v>6992226</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404703</v>
+        <v>122404640</v>
       </c>
       <c r="B2" t="n">
         <v>79737</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563830</v>
+        <v>563708</v>
       </c>
       <c r="R2" t="n">
-        <v>6992367</v>
+        <v>6992337</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404733</v>
+        <v>122404710</v>
       </c>
       <c r="B3" t="n">
         <v>79737</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563908</v>
+        <v>563830</v>
       </c>
       <c r="R3" t="n">
-        <v>6992177</v>
+        <v>6992367</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404640</v>
+        <v>122404662</v>
       </c>
       <c r="B4" t="n">
         <v>79737</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563708</v>
+        <v>563938</v>
       </c>
       <c r="R4" t="n">
-        <v>6992337</v>
+        <v>6992226</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404662</v>
+        <v>122404733</v>
       </c>
       <c r="B5" t="n">
         <v>79737</v>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563938</v>
+        <v>563908</v>
       </c>
       <c r="R5" t="n">
-        <v>6992226</v>
+        <v>6992177</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404640</v>
+        <v>122404662</v>
       </c>
       <c r="B2" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563708</v>
+        <v>563938</v>
       </c>
       <c r="R2" t="n">
-        <v>6992337</v>
+        <v>6992226</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404710</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563830</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992367</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404662</v>
+        <v>122404640</v>
       </c>
       <c r="B4" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563938</v>
+        <v>563708</v>
       </c>
       <c r="R4" t="n">
-        <v>6992226</v>
+        <v>6992337</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404733</v>
+        <v>122404703</v>
       </c>
       <c r="B5" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563908</v>
+        <v>563830</v>
       </c>
       <c r="R5" t="n">
-        <v>6992177</v>
+        <v>6992367</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122404662</v>
       </c>
       <c r="B2" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404733</v>
+        <v>122404640</v>
       </c>
       <c r="B3" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563908</v>
+        <v>563708</v>
       </c>
       <c r="R3" t="n">
-        <v>6992177</v>
+        <v>6992337</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404640</v>
+        <v>122404733</v>
       </c>
       <c r="B4" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563708</v>
+        <v>563908</v>
       </c>
       <c r="R4" t="n">
-        <v>6992337</v>
+        <v>6992177</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -984,7 +984,7 @@
         <v>122404703</v>
       </c>
       <c r="B5" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404662</v>
+        <v>122404674</v>
       </c>
       <c r="B2" t="n">
         <v>79741</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122404640</v>
+        <v>122404733</v>
       </c>
       <c r="B3" t="n">
         <v>79741</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563708</v>
+        <v>563908</v>
       </c>
       <c r="R3" t="n">
-        <v>6992337</v>
+        <v>6992177</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122404733</v>
+        <v>122404640</v>
       </c>
       <c r="B4" t="n">
         <v>79741</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563908</v>
+        <v>563708</v>
       </c>
       <c r="R4" t="n">
-        <v>6992177</v>
+        <v>6992337</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404703</v>
+        <v>122404710</v>
       </c>
       <c r="B5" t="n">
         <v>79741</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på granit</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,6 +1086,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125112589</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storsjöflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563912</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6992297</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>125112589</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -1091,12 +1091,7 @@
         <v>125112589</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122404733</v>
+        <v>122404640</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563908</v>
+        <v>563708</v>
       </c>
       <c r="R2" t="n">
-        <v>6992177</v>
+        <v>6992337</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -780,12 +775,7 @@
         <v>122404662</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,12 +872,7 @@
         <v>122404703</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122404640</v>
+        <v>122404733</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563708</v>
+        <v>563908</v>
       </c>
       <c r="R5" t="n">
-        <v>6992337</v>
+        <v>6992177</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,7 +1071,7 @@
         <v>125112589</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2024 artfynd.xlsx
+++ b/artfynd/A 6906-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122404640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122404662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122404703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122404733</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,8 +1187,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125112589</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>